--- a/Universities-Verified.xlsx
+++ b/Universities-Verified.xlsx
@@ -159,10 +159,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -560,14 +560,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>جدول اصلاح‌شده و راستی‌آزمی‌شده — ۷ دانشگاه کانادا (نسخهٔ معتبر)</t>
+          <t>جدول اصلاح‌شده و راستی‌آزمی‌شده — ۸ دانشگاه کانادا (۷ ردیف فایل شما + Guelph)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>۱ اکتبر ۲۰۲۶ · ورودی هدف سپتامبر ۲۰۲۷ · بودجه $40,000 کل دوره در دو گام (گام۱ = شهریهٔ کل دوره + تمکن رسمی $16,500 آنچه سفارت می‌بیند؛ گام۲ = زندگی واقعی + کار ۲۴ ساعت/هفته) · نرخ ارز CAD 1 = USD 0.705 · رتبه‌ها: QS 2027 (ژوئن ۲۰۲۶) · «≈» یعنی رقم از منبع ثانویه است و قبل از اپلای باید با صفحهٔ رسمی چک شود · درصدهای ستون شانس با * خام و کالیبره‌نشده‌اند (مثل چک‌لیست کانادا) و فقط برای مقایسه‌اند.</t>
+          <t>۱ اکتبر ۲۰۲۶ (ردیف ۸ Guelph: ۲ اکتبر ۲۰۲۶) · ورودی هدف سپتامبر ۲۰۲۷ · بودجه $40,000 کل دوره در دو گام (گام۱ = شهریهٔ کل دوره + تمکن رسمی $16,500 آنچه سفارت می‌بیند؛ گام۲ = زندگی واقعی + کار ۲۴ ساعت/هفته) · نرخ ارز CAD 1 = USD 0.705 · رتبه‌ها: QS 2027 (ژوئن ۲۰۲۶) · «≈» یعنی رقم از منبع ثانویه است و قبل از اپلای باید با صفحهٔ رسمی چک شود · درصدهای ستون شانس با * خام و کالیبره‌نشده‌اند (مثل چک‌لیست کانادا) و فقط برای مقایسه‌اند.</t>
         </is>
       </c>
     </row>
@@ -783,9 +783,10 @@
           <t>uOttawa — اتاوا، انتاریو</t>
         </is>
       </c>
-      <c r="C7" s="5">
-        <f>228 (فایل: ~۱۸۰–۲۰۰ ← قدیمی؛ از ~۱۸۹ در ۲۰۲۶ افت کرده)</f>
-        <v/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>=228 (فایل: ~۱۸۰–۲۰۰ ← قدیمی؛ از ~۱۸۹ در ۲۰۲۶ افت کرده)</t>
+        </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -849,9 +850,10 @@
           <t>McMaster — همیلتون، انتاریو</t>
         </is>
       </c>
-      <c r="C8" s="8">
-        <f>174 (فایل: ~۱۸۰ ← تقریباً درست)</f>
-        <v/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>=174 (فایل: ~۱۸۰ ← تقریباً درست)</t>
+        </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -982,9 +984,10 @@
           <t>UVic — ویکتوریا، بریتیش کلمبیا</t>
         </is>
       </c>
-      <c r="C10" s="8">
-        <f>370 (فایل: ~۳۵۰–۴۰۰ ← درست)</f>
-        <v/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>=370 (فایل: ~۳۵۰–۴۰۰ ← درست)</t>
+        </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>شهریهٔ کل ≈ $42,800 + $16,500 = $59,300 ❌ (بدترین گام۱ بین این هفت‌تا)</t>
+          <t>شهریهٔ کل ≈ $42,800 + $16,500 = $59,300 ❌ (بدترین گام۱ بین این هشت‌تا)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1104,17 +1107,84 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>راهنما: ✅ داخل بودجه در گام۱ (آنچه سفارت می‌بیند) · ❌ بیرون بودجه در گام۱ · ⚠️ مشروط/نیازمند تأیید. ستون «مسیر جایگزین» مهم‌ترین ستون این فایل است: در کانادا مسیر پایان‌نامه‌ای (با فاندینگ) معمولاً ارزان‌تر از مسیر درسیِ همین دانشگاه است — چیزی که فایل قبلی شما کلاً نداشت. بودجهٔ نهایی شما $40,000 برای کل دوره است، نه ۳۲ هزار دلار در سال که فایل قبلی فرض کرده بود.</t>
+    <row r="12" ht="250" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Guelph — گوئلف، انتاریو</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>=546 در QS 2027 (QS 2026: 504) · THE 2027: 451–500 · THE Computer Science 2026: 301–400 (ردیف جدید؛ در فایل اصلی نبود). از این جدول فقط Carleton هم‌رده‌اش است.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>پایان‌نامه‌ای (مسیر اصلی و داخل بودجه): ① MASc مهندسی — حوزهٔ Computer Engineering یا Engineering Systems &amp; Computing (College of Engineering، ۲۴ ماه)؛ ② MSc Computer Science (School of Computer Science، ۲۴ ماه؛ ۱۶ ماه هم ممکن است). هر دو بدون استاد راهنما پذیرش نمی‌دهند. درسی: MEng کامپیوتر/ESC (۱۲–۱۶ ماه) — خارج بودجه. MCTI/MCLC امنیت‌اند (طبق خواستهٔ شما کنار گذاشته شد) و MDS گران است.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>MSc و MASc کوآپ ندارند؛ درآمد عملاً GTA/GRA روی کمپوس است. MEng فقط یک WEX اختیاری دارد (از سپتامبر ۲۰۲۶؛ حقوق‌دار، حدود ۴ ماه، حداقل ۱۰ هفته و ۳۵۰ ساعت، با سه درس WEX) — نوع مجوز کار آن را قبل از اپلای از دانشگاه بپرسید.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>6.5 کلی؛ مهندسی: هیچ بخشی زیر 6.0 (آیلتس 7.0 فرضی شما بالاتر از کف است)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>MSc: ≥۷۵٪ (B) در دو سال آخر + مدرک CS یا ≥۱۰ درس CS. MASc: ≥۷۵٪ در ۴ ترم آخر + مدرک مهندسی. معادل‌سازی را خود Guelph با جدول Scholaro انجام می‌دهد (برای MASc: WES قبول نیست): ۱۴–۱۶.۹۹ = B و ۱۷+ = A → ۱۶.۹۲ شما فقط ۰.۰۸ زیر A است؛ کف را رد می‌کنید ولی «A−» دیده نمی‌شوید → Target</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>رسمی ۲۰۲۶/۲۷: MSc/MASc = CAD 6,837.54 هر ترم (CAD 20,512 در سال)؛ ۲۴ ماه (۶ ترم) = CAD 41,025. + هزینهٔ اجباری CAD 2,216/سال + UHIP CAD 792/سال. شهریهٔ ۲۰۲۷/۲۸ MSc/MASc هنوز منتشر نشده؛ برای MEng رسماً ≈ +۱۰٪ شده (CAD 39,325 ← 43,241).</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>≈ 32,400 قبل از فاندینگ (شهریه ≈ 14,500 + اجباری و UHIP ≈ 2,100 + زندگی ≈ 15,900 طبق برآورد رسمی دانشگاه، CAD 22,494/سال). خالص بعد از فاندینگ حداقلی: MSc ≈ 18,300 · MASc ≈ 7,400–15,900</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ مشروط به نامهٔ فاندینگ. بدون آن: شهریهٔ ۲ سال $28,900 + اجباری/UHIP $4,200 + تمکن $16,500 ≈ $49,700 ❌ (فقط‌شهریه، هم‌پایه با ردیف‌های قبلی: $45,400). با فاندینگ: MASc ≈ $16,500–16,700 ✅✅ · MSc ≈ $21,500 ✅؛ گام۲ هم بسته است (کل ۲۴ ماه زندگی از $40k، بدون هیچ کار اضافه). MEng ≈ $49,100 ❌.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>خود مسیر پایان‌نامه‌ای است: MASc کامپیوتر/ESC (فاندینگ در نامهٔ Offer) یا MSc CS با استاد HCI/AI کاربردی. خارج بودجه: MEng ≈ $49,100 · MDS ≥ $52,900 · MCTI ≈ $54,600 · MCLC ≈ $61,000 (دو تای آخر امنیت‌اند).</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>MSc و MASc ≈ ۳۰–۵۰٪* (گلوگاه: «بله»ی استاد) · MEng ≈ ۶۵–۸۵٪* ولی خارج بودجه</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>بین‌المللی، Fall 2027: MSc ۱ مارس ۲۰۲۷؛ MASc ۱۵ آوریل (بالای صفحه) یا ۱۵ مارس (جدول ۲۰۲۶ همان صفحه) — ناهماهنگ، ۱ مارس را مبنا بگیرید. تصمیم ۲–۳ ماه + ویزا ۲۰–۳۰ هفته → عملاً اپلای دسامبر ۲۰۲۶ تا ژانویه ۲۰۲۷ و ایمیل استاد از همین الان. برنامهٔ ب: Winter 2028 (SoCS: ۱ اوت ۲۰۲۷). اپلیکیشن‌فی CAD 125. تخصص مشترک AI (Vector): بورس CAD 17,500 رقابتی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>راهنما: ✅ داخل بودجه در گام۱ (آنچه سفارت می‌بیند) · ❌ بیرون بودجه در گام۱ · ⚠️ مشروط/نیازمند تأیید. ستون «مسیر جایگزین» مهم‌ترین ستون این فایل است: در کانادا مسیر پایان‌نامه‌ای (با فاندینگ) معمولاً ارزان‌تر از مسیر درسیِ همین دانشگاه است — چیزی که فایل قبلی شما کلاً نداشت. بودجهٔ نهایی شما $40,000 برای کل دوره است، نه ۳۲ هزار دلار در سال که فایل قبلی فرض کرده بود. ردیف ۸ (Guelph) در فایل اصلی شما نبود و بعداً اضافه شد؛ برخلاف ردیف‌های ۱–۷ (فقط شهریه)، گام۱ آن هزینهٔ اجباری و UHIP را هم دارد؛ رنگ زرد یعنی «مشروط به نامهٔ فاندینگ».</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A13:M13"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1127,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1253,7 +1323,7 @@
           <t>≈ $۲۱.۵–۲۴k (شهریه رسمی $۷.۴k + زندگی ادمونتون)</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>⚠️ زیاد</t>
         </is>
@@ -1280,7 +1350,7 @@
           <t>کف روی ۶۰ واحد آخر (دو سال آخر شما ۱۶.۹۲) سنجیده می‌شود؛ بازهٔ واقع‌بینانه ۴۰–۶۰٪*</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>⚠️ خوش‌بینانه</t>
         </is>
@@ -1334,7 +1404,7 @@
           <t>MEng برق و کامپیوتر با گرایش نرم‌افزار</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>⚠️ نادرست</t>
         </is>
@@ -1361,7 +1431,7 @@
           <t>۸ تا ۱۶ ماه، ظرفیت محدود، بعد از یک سال تحصیل؛ دوره را ۳ ساله می‌کند</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>⚠️ نیمه‌درست</t>
         </is>
@@ -1437,9 +1507,10 @@
           <t>~۱۸۰–۲۰۰</t>
         </is>
       </c>
-      <c r="D14" s="8">
-        <f>۲۲۸ در QS 2027</f>
-        <v/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>=۲۲۸ در QS 2027</t>
+        </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -1468,7 +1539,7 @@
           <t>کوآپ ارشد اختیاری/ظرفیت محدود/رقابت معدل؛ «دوم انتاریو» ادعای خود دانشگاه دربارهٔ کوآپ کارشناسی است</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>⚠️ گمراه‌کننده</t>
         </is>
@@ -1495,7 +1566,7 @@
           <t>≈ $۳۰–۳۲k با شهریه سال اول ~$۱۸.۱k و زندگی اتاوا</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>⚠️ کمی زیاد</t>
         </is>
@@ -1517,9 +1588,10 @@
           <t>~۱۸۰</t>
         </is>
       </c>
-      <c r="D17" s="5">
-        <f>۱۷۴ در QS 2027</f>
-        <v/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>=۱۷۴ در QS 2027</t>
+        </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -1575,7 +1647,7 @@
           <t>≈ $۲۸.۶–۳۰.۵k</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>⚠️ زیاد</t>
         </is>
@@ -1629,7 +1701,7 @@
           <t>۲۹۸ در QS 2027</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>⚠️ کمی قدیمی</t>
         </is>
@@ -1732,9 +1804,10 @@
           <t>~۳۵۰–۴۰۰</t>
         </is>
       </c>
-      <c r="D25" s="5">
-        <f>۳۷۰ در QS 2027</f>
-        <v/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>=۳۷۰ در QS 2027</t>
+        </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -1763,7 +1836,7 @@
           <t>کوآپ ارشد اختیاری وجود دارد؛ «قوی‌ترین» قابل سنجش نیست ولی کوآپ بزرگی دارند</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>⚠️ نیمه‌درست</t>
         </is>
@@ -1817,7 +1890,7 @@
           <t>≈ ۵۵۰–۶۰۰ (در QS 2026 = ۵۶۰)؛ قدرت مهندسی سیستم درست است</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>⚠️ کمی خوش‌بینانه</t>
         </is>
@@ -1880,27 +1953,27 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>همه</t>
+          <t>Guelph</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>سقف بودجه</t>
+          <t>ردیف جدید</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>$۳۲ هزار</t>
+          <t>(در فایل شما نبود)</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>مدل نهایی ما $۴۰ هزار برای کل دوره در دو گام است (بخش ۲۱–۲۲ تحلیل اصلی)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>❌ منسوخ</t>
+          <t>ردیف ۸ با همان قالب و همان مدل بودجه اضافه شد: =546 در QS 2027؛ فقط مسیر پایان‌نامه‌ای با فاندینگ (MASc/MSc) داخل بودجه است؛ MEng و بقیه خارج</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>✅ افزوده شد</t>
         </is>
       </c>
     </row>
@@ -1912,22 +1985,22 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>مبنای معدل</t>
+          <t>سقف بودجه</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>فقط سال آخر (~۱۷)</t>
+          <t>$۳۲ هزار</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>هیچ‌کدام از این دانشگاه‌ها فقط سال آخر را نمی‌سنجند: آلبرتا/کلگری/دالهاوزی = ۶۰ واحد آخر (۱۶.۹۲ شما)، بقیه کل یا دو سال آخر</t>
+          <t>مدل نهایی ما $۴۰ هزار برای کل دوره در دو گام است (بخش ۲۱–۲۲ تحلیل اصلی)</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>❌ فرض غلط</t>
+          <t>❌ منسوخ</t>
         </is>
       </c>
     </row>
@@ -1939,20 +2012,47 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>مبنای معدل</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>فقط سال آخر (~۱۷)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>هیچ‌کدام از این دانشگاه‌ها فقط سال آخر را نمی‌سنجند: آلبرتا/کلگری/دالهاوزی = ۶۰ واحد آخر (۱۶.۹۲ شما)، بقیه کل یا دو سال آخر</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>❌ فرض غلط</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>همه</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>ستون نمره‌دهی</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>صفت‌هایی مثل «منصفانه و تعاملی»</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>نه منبعی دارد نه تعریف مشخصی؛ قابل راستی‌آزمایی نیست و حذف شد</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>❌ بی‌محتوا</t>
         </is>
@@ -1973,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1994,7 +2094,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>در کانادا معمولاً ارشد پایان‌نامه‌ای همان دانشگاه از نسخهٔ درسی‌اش ارزان‌تر و با فاندینگ همراه است. اعداد رسمی 2026/27 از تحلیل قبلی (بخش ۲۸) و منابع رسمی.</t>
+          <t>در کانادا معمولاً ارشد پایان‌نامه‌ای همان دانشگاه از نسخهٔ درسی‌اش ارزان‌تر و با فاندینگ همراه است. اعداد رسمی 2026/27 از تحلیل قبلی (بخش ۲۸) و منابع رسمی؛ ردیف‌های Guelph از صفحه‌های رسمی خود دانشگاه (۲ اکتبر ۲۰۲۶) و برای دو مسیرِ داخل بودجهٔ آن است.</t>
         </is>
       </c>
     </row>
@@ -2251,6 +2351,70 @@
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>کارلتون با بودجهٔ شما عملاً بیرون است؛ همجواری کاناتا ارزش رزومه دارد ولی جای بودجه را پر نمی‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>MASc مهندسی — کامپیوتر / Engineering Systems &amp; Computing (پایان‌نامه‌ای، ۲ سال)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>≈ $33,200 (شهریه $28,900 + اجباری/UHIP $4,200؛ رسمی ۲۰۲۶/۲۷)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>≈ $16,500–16,700 ✅✅ با فاندینگ؛ $49,700 ❌ بدون آن</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>حداقل تضمینیِ بستهٔ Offer: CAD 23,400 (صفحهٔ Funding، S25+) یا CAD 35,500 (صفحهٔ برنامه، S26+) در سال × ۲ سال — دو صفحهٔ رسمی ناهماهنگ</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>مناسب‌ترین گزینهٔ Guelph برای مدرک مهندسی کامپیوتر و نمرات نرم‌افزار/OS. کف: ۷۵٪ در ۴ ترم آخر؛ IELTS 6.5 (هر بخش ≥ 6.0)؛ WES قبول نیست. گلوگاه: «بله»ی استاد + ویزا؛ فاندینگ قطعی را فقط نامهٔ Offer نشان می‌دهد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="165" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>MSc Computer Science (پایان‌نامه‌ای، ۲ سال)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>≈ $33,200 (همان؛ شهریهٔ ۲۰۲۷/۲۸ هنوز منتشر نشده)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ مشروط: $21,500 ✅ با فاندینگ (کسری خالص ≈ $5,000)؛ $49,700 ❌ بدون آن</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>حداقل CAD 20,000 در سال (حداکثر ۲ سال) برای بین‌المللی‌های دارای استاد؛ فقط در صفحهٔ برنامه آمده — صفحهٔ Funding خود SoCS برای بین‌المللی‌های MSc چیزی نمی‌گوید</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>گروه‌های AI/ML، HCI، دیتا و بیوانفورماتیک (امنیت کنار گذاشته شد)؛ مهندسی نرم‌افزار/سیستم جزو حوزه‌های SoCS نیست. تخصص مشترک AI (Vector): بورس CAD 17,500 رقابتی؛ ۱۶.۹۲ در جدول Scholaro «B» است، نه A.</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2280,7 +2444,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>منابع راستی‌آزمی (بازدید ۱ اکتبر ۲۰۲۶)</t>
+          <t>منابع راستی‌آزمی (بازدید ۱ اکتبر ۲۰۲۶؛ منابع Guelph: ۲ اکتبر ۲۰۲۶)</t>
         </is>
       </c>
     </row>
@@ -2651,32 +2815,338 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>تمکن مالی مجوز تحصیل — $16,500 (سپتامبر ۲۰۲۶، خارج کبک)</t>
+          <t>Guelph — رتبهٔ QS 2027 (=546)</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/en/immigration-refugees-citizenship/services/study-canada/study-permit/prepare/proof-funds.html</t>
+          <t>https://www.topuniversities.com/universities/university-guelph</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>رسمی</t>
+          <t>رسمیِ رتبه‌بند</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
+          <t>Guelph — THE 2027 (451–500) و THE Computer Science 2026 (301–400)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>https://www.timeshighereducation.com/world-university-rankings/university-guelph</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — رتبهٔ QS 2026 (504)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/cbs/news/2026/03/university-guelph-retains-global-ranking-biological-sciences-anatomy-physiology-2026-qs</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — MSc Computer Science (شرایط، ددلاین‌های ۲۰۲۷، فاندینگ CAD 20,000)</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/msc-computer-science</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — MASc مهندسی (شرایط، ددلاین، IELTS، فاندینگ S26+ = CAD 35,500)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/masc-engineering/</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — فاندینگ مهندسی (S25+ = CAD 23,400؛ MEng بدون فاندینگ)</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/engineering/future/graduate-funding/</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — MEng (۱۲–۱۶ ماه، WEX اختیاری، ددلاین‌ها، کف ۷۰٪)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/master-of-engineering/</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — WEX (حداقل ۱۰ هفته و ۳۵۰ ساعت، سه درس)</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/experiential-learning/current-students/wex</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — Master of Data Science (درسی، ۱۲–۱۶ ماه)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/master-of-data-science</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول شهریهٔ سالانهٔ ۲۰۲۶/۲۷ و ۲۰۲۷/۲۸، برآورد هزینهٔ زندگی، UHIP، خوابگاه</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/cost</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — شهریهٔ هر ترم و هزینه‌های اجباری ۲۰۲۶/۲۷</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/registrar/finances-fees/tuition-fees/guelph-grad</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول نمرات زبان انگلیسی</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/international/english</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — معادل‌سازی مدرک ایران (کارشناسی ۴ ساله پذیرفته)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/international/credential</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول نمره‌دهی ایران (Scholaro: B = 14–16.99؛ مرجعِ ارجاعیِ خود Guelph)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>https://www.scholaro.com/db/Countries/Iran/Grading-System</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — مراحل اپلای و اپلیکیشن‌فی CAD 125</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/applying-guelph</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — مدارک اپلای (اعتبار ۲ سالهٔ نمرهٔ زبان، ترجمهٔ رسمی)</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/apply/documents</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — حوزه‌های تحقیقاتی و استادهای SoCS</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/computing/future/graduate-studies/</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — تخصص مشترک AI و بورس Vector (CAD 17,500)</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/csai/</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>تمکن مالی مجوز تحصیل — $16,500 (سپتامبر ۲۰۲۶، خارج کبک)</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/immigration-refugees-citizenship/services/study-canada/study-permit/prepare/proof-funds.html</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
           <t>تحلیل کامل قبلی (بخش ۲۸: کانادا با اعداد رسمی)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Migration-Analysis.md در همین ریپو</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>داخلی</t>
         </is>
@@ -2697,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2790,7 +3260,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="62" customHeight="1">
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>هزینهٔ زندگی</t>
@@ -2798,7 +3268,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>بازه‌های ماهانهٔ شیت «خوابگاه و مسکن» تحلیل قبلی: ادمونتون $1,500–1,800 · کلگری $1,650–2,000 · اتاوا $1,800–2,200 · همیلتون $1,400–1,700 · هالیفاکس $1,650–2,000 · ویکتوریا $1,900–2,300 (دلار کانادا) × ۱۲ ماه.</t>
+          <t>بازه‌های ماهانهٔ شیت «خوابگاه و مسکن» تحلیل قبلی: ادمونتون $1,500–1,800 · کلگری $1,650–2,000 · اتاوا $1,800–2,200 · همیلتون $1,400–1,700 · هالیفاکس $1,650–2,000 · ویکتوریا $1,900–2,300 · گوئلف $1,800–1,900 (برآورد رسمی دانشگاه: CAD 22,494 در سال) (دلار کانادا) × ۱۲ ماه.</t>
         </is>
       </c>
     </row>
@@ -2838,15 +3308,63 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="62" customHeight="1">
+    <row r="14" ht="135" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>Guelph — مبنای گام۱</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>برخلاف ردیف‌های ۱–۷ که فقط شهریه داشتند، برای Guelph هزینهٔ اجباری رسمی (CAD 2,215.56 در سال: پاییز 937.21 + زمستان 642.80 + تابستان 635.55) و بیمهٔ UHIP (CAD 792 در سال) هم در گام۱ آمده، چون رسمی و بزرگ‌اند (≈ $4,200 برای ۲ سال). شهریهٔ ۶ ترم = 6 × CAD 6,837.54 = CAD 41,025 ≈ $28,900 (نرخ ۲۰۲۶/۲۷؛ نرخ ورودی ۲۰۲۷ هنوز منتشر نشده — با +۱۰٪، گام۱ با فاندینگ MSc ≈ $24,400 می‌شود و باز داخل بودجه است). برای مقایسهٔ هم‌پایه با ردیف‌های قبلی: فقط شهریه و بدون فاندینگ = $28,900 + $16,500 = $45,400. زندگی: برآورد رسمی دانشگاه CAD 22,494 در سال ≈ CAD 1,875 در ماه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Guelph — فاندینگ</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>«با فاندینگ» یعنی نامهٔ رسمی فاندینگ دست شماست؛ تا آن موقع عدد بدون فاندینگ ($49,700 ❌) مبناست. MASc: صفحهٔ برنامهٔ College of Engineering برای شروع از S26 به بعد حداقل CAD 35,500 در سال (۲ سال) می‌گوید، ولی صفحهٔ Funding همان کالج هنوز CAD 23,400 (S25+) دارد؛ مبنای محافظه‌کارانهٔ این فایل CAD 23,400 است (گام۱ ≈ $16,700). MSc: CAD 20,000 در سال (حداکثر ۲ سال) فقط در صفحهٔ برنامهٔ MSc آمده و صفحهٔ Funding خود SoCS برای بین‌المللی‌های MSc چنین قولی نمی‌دهد. در محاسبه، فاندینگ بیش از شهریه + هزینهٔ اجباری + UHIP حساب نشده (مثل Calgary) و قبل از مالیات/CPP است. هر دو مسیر به پذیرفته‌شدن توسط یک استاد وابسته‌اند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="95" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Guelph — معدل و نمرهٔ ایران</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Guelph معادل‌سازی را خودش انجام می‌دهد (در MASc، WES پذیرفته نمی‌شود) و برای جدول نمره‌دهی کشورها به Scholaro ارجاع می‌دهد: ایران ۱۸–۲۰ = A+، ۱۷–۱۷.۹۹ = A، ۱۴–۱۶.۹۹ = B. دو سال آخر شما ۱۶.۹۲ است، یعنی ۰.۰۸ زیر مرز A؛ کف ۷۵٪ (B) را رد می‌کند ولی در معیارهایی که A− می‌خواهند (مثل Vector Scholarship، طبق منابع قدیمی‌تر؛ معیار فعلی را چک کنید) مرزی است. معادل‌سازی نهایی با دفتر تحصیلات تکمیلی Guelph است، نه با این فایل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="95" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Guelph — ناهماهنگی صفحه‌های رسمی</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>ددلاین MASc: بالای صفحه ۱۵ آوریل (بین‌المللی، Fall) ولی جدول ۲۰۲۶ همان صفحه ۱۵ مارس؛ SoCS برای Fall 2027 صریحاً ۱ مارس ۲۰۲۷ نوشته. مبنای ما: ۱ مارس. مدارک MASc تا یک ماه بعد از ددلاین پذیرفته می‌شود ولی توصیهٔ رسمی، اپلای ≥ ۹ ماه قبل از شروع است. خوابگاه تضمینی برای بین‌المللی‌ها در دادهٔ ۲۰۲۶ بود (درخواست و ودیعه تا ۱ ژوئن)؛ برای ۲۰۲۷ دوباره چک شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>آنچه این فایل نیست</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>این فایل جایگزین چک‌لیست کانادا و شیت «تصمیم» در Table_final.xlsx نیست؛ فقط نسخهٔ اصلاح‌شدهٔ همان جدول ۷ ردیفی شماست. هشت درخواست اروپایی و مسیر پایان‌نامه‌ای موازات کانادا (تحلیل بخش ۲۸) سر جای خودشان باقی‌اند.</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>این فایل جایگزین چک‌لیست کانادا و شیت «تصمیم» در Table_final.xlsx نیست؛ فقط نسخهٔ اصلاح‌شدهٔ همان جدول ۷ ردیفی شماست. هشت درخواست اروپایی و مسیر پایان‌نامه‌ای موازات کانادا (تحلیل بخش ۲۸) سر جای خودشان باقی‌اند. ردیف ۸ (Guelph) بعداً، ۲ اکتبر ۲۰۲۶، به درخواست شما اضافه شد.</t>
         </is>
       </c>
     </row>

--- a/Universities-Verified.xlsx
+++ b/Universities-Verified.xlsx
@@ -10,8 +10,10 @@
     <sheet name="جدول اصلاح‌شده" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="مقایسه با فایل قبلی" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="مسیرهای جایگزین" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="منابع" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مفروضات و هشدارها" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="خوابگاه" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="خوابگاه — قیمت‌ها" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="منابع" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="مفروضات و هشدارها" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -168,10 +170,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1174,10 +1176,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="62" customHeight="1">
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>راهنما: ✅ داخل بودجه در گام۱ (آنچه سفارت می‌بیند) · ❌ بیرون بودجه در گام۱ · ⚠️ مشروط/نیازمند تأیید. ستون «مسیر جایگزین» مهم‌ترین ستون این فایل است: در کانادا مسیر پایان‌نامه‌ای (با فاندینگ) معمولاً ارزان‌تر از مسیر درسیِ همین دانشگاه است — چیزی که فایل قبلی شما کلاً نداشت. بودجهٔ نهایی شما $40,000 برای کل دوره است، نه ۳۲ هزار دلار در سال که فایل قبلی فرض کرده بود. ردیف ۸ (Guelph) در فایل اصلی شما نبود و بعداً اضافه شد؛ برخلاف ردیف‌های ۱–۷ (فقط شهریه)، گام۱ آن هزینهٔ اجباری و UHIP را هم دارد؛ رنگ زرد یعنی «مشروط به نامهٔ فاندینگ».</t>
+          <t>راهنما: ✅ داخل بودجه در گام۱ (آنچه سفارت می‌بیند) · ❌ بیرون بودجه در گام۱ · ⚠️ مشروط/نیازمند تأیید. ستون «مسیر جایگزین» مهم‌ترین ستون این فایل است: در کانادا مسیر پایان‌نامه‌ای (با فاندینگ) معمولاً ارزان‌تر از مسیر درسیِ همین دانشگاه است — چیزی که فایل قبلی شما کلاً نداشت. بودجهٔ نهایی شما $40,000 برای کل دوره است، نه ۳۲ هزار دلار در سال که فایل قبلی فرض کرده بود. ردیف ۸ (Guelph) در فایل اصلی شما نبود و بعداً اضافه شد؛ برخلاف ردیف‌های ۱–۷ (فقط شهریه)، گام۱ آن هزینهٔ اجباری و UHIP را هم دارد؛ رنگ زرد یعنی «مشروط به نامهٔ فاندینگ». خوابگاه هر ۸ دانشگاه (تضمین، ددلاین، ودیعه، قیمت 2026–27 با منبع) در شیت‌های «خوابگاه» و «خوابگاه — قیمت‌ها» است؛ در گام۱ نیست و در گام۲ (زندگی واقعی) می‌آید.</t>
         </is>
       </c>
     </row>
@@ -2433,729 +2435,656 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>منابع راستی‌آزمی (بازدید ۱ اکتبر ۲۰۲۶؛ منابع Guelph: ۲ اکتبر ۲۰۲۶)</t>
+          <t>خوابگاه ارشد — ۸ دانشگاه: چه دارند، تضمین هست یا نه، کی اپلای، چقدر پیش‌پرداخت، ودیعه با رد ویزا چه می‌شود</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«رسمی» = صفحهٔ خود دانشگاه یا نهاد دولتی · «ثانویه» = سرویس‌های اپلای/اطلاعات دوره (شیکشا، مسترزپورتال، کالج‌دونیا، اپلای‌بورد، آی‌دی‌پی) — برای اپلای با صفحهٔ رسمی چک شود.</t>
+          <t>بازدید ۲ اکتبر ۲۰۲۶ · فقط صفحه‌های رسمی خودِ دانشگاه‌ها · ورودی هدف سپتامبر ۲۰۲۷ (تاریخ‌های ۲۰۲۷ از صفحه‌های امسال؛ هر جا نیست «تأییدنشده» نوشته شده) · نتیجه: در هر ۸ دانشگاه خوابگاه جدا از شهریه است (قرارداد، ودیعه و صورت‌حساب جدا) و در گام۲ بودجه می‌آید، نه گام۱ · تضمین برای ارشدِ بین‌المللی فقط در Guelph است · قیمت‌ها در شیت «خوابگاه — قیمت‌ها».</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>موضوع</t>
+          <t>ردیف</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>نشانی</t>
+          <t>دانشگاه</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>وضع منبع</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>خوابگاه مناسب ارشد (چه دارند)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>تضمین برای ارشدِ بین‌المللی؟</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>جدا از شهریه؟ (صورت‌حساب و شمول)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>شروع درخواست و ددلاین (Fall 2027)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت و بازپرداخت (ودیعه ← رد ویزا)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>قرارداد و تابستان</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>تأییدنشده / نکته</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>منابع رسمی</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>تاریخ بازدید</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="175" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>رتبهٔ آلبرتا — ۹۶ (QS 2027)</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-alberta</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>رسمیِ رتبه‌بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>۱</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Alberta — ادمونتون</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>• Graduate Residence — فقط ارشد؛ ۴ ساختمان (Rockcress، Stonecrop، Juniper، Speedwell)؛ واحد مبلهٔ مشترک یا استودیو که تک‌تک اجاره می‌شود
+• HUB — ارشد و کارشناسیِ سال‌بالا؛ استودیو و یک‌خوابه (زوج‌ها در یک‌خوابه)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — تضمین فقط برای «سال اول کارشناسی» است (ددلاین ۳۰ آوریل)
+• ارشد: انتخاب ساختمان و اتاق با time slot است و ترتیبش به تاریخ درخواست بستگی دارد؛ پس زود اپلای کنید</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>جدا — اجارهٔ ماهانه/قرارداد خوابگاه، نه بخشی از شهریه یا هزینه‌های اجباری؛ روش صورت‌حساب در صفحه‌ها نیامده
+• HUB: اجاره شامل اینترنت بی‌سیم، گرما، آب و برق است</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>• الان باز است: Fall 2027 و Winter 2028
+• برای فرم فقط CCID لازم است؛ بعد از ثبت درخواست برنامه ≤ ۷۲ ساعت صادر می‌شود و پذیرش لازم نیست
+• پیشنهاد اتاق: اواخر بهار (ایمیل دانشگاه)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>• درخواست CAD 25 (غیرقابل‌برگشت)
+• ودیعهٔ CAD 500 برای قبول offer (= اجارهٔ ماه اول؛ غیرقابل‌برگشت)
+• ✅ اگر ویزا رد شود ودیعه برمی‌گردد: ظرف ۱۰ روز از اطلاع، با نامهٔ رد و پیش از move-in
+• لغو بدون جریمهٔ قرارداد تا ۳۱ ژوئیه (Fall)؛ بعد از گرفتن کلید باید اجارهٔ باقی‌ماندهٔ قرارداد را بدهید (+ یک ماه اگر کمتر از ۳۰ روز خبر بدهید)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>• Graduate Residence: قرارداد سالانه تا ۳۱ جولای (اولی ۱۱ ماه، تمدیدها ۱۲ ماه)
+• HUB: استودیو و یک‌خوابه ماه‌به‌ماه؛ ۲ و ۴ خوابه ۸ ماهه (+ تابستان ۲–۴ ماهه)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ صفحهٔ Unit Types سال نرخ ندارد؛ نرخ صفحهٔ خود Graduate Residence لود نشد؛ شمول قبوض فقط در HUB تصریح شده
+⚠️ همان صفحه می‌گوید فقط «current U of A students» واجدند — از housing@ualberta.ca بپرسید دانشجوی جدید ارشد پیش از پذیرش می‌تواند یا نه</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/unit-types.html
+https://www.ualberta.ca/en/residence/our-residences/graduate-residence.html
+https://www.ualberta.ca/en/residence/our-residences/hub.html
+https://www.ualberta.ca/en/residence/apply/index.html
+https://www.ualberta.ca/en/residence/apply/guaranteed-housing.html
+https://www.ualberta.ca/en/residence/apply/cancellation-policy.html</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>رتبهٔ کلگری — ۲۴۹ (QS 2027)</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-calgary</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>رسمیِ رتبه‌بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>۲</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Calgary — کلگری</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>• Crowsnest Hall — برای ارشد، دارندگان مدرک کارشناسی و mature (۲۷+ سال)؛ استودیو، یک‌خوابه و دوخوابه با آشپزخانهٔ کامل</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — قرعه؛ صفحه صریح می‌گوید تضمین نمی‌کند که متقاضی offer بگیرد
+• تضمین فقط برای سال‌اولیِ تازه‌دیپلمه (زیر ۲۱ سال) با درخواست تا ۱ مه</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>جدا — قسط‌های خوابگاه (سیکل 2026–27: ۱۸ سپتامبر و ۲۹ ژانویه) مستقل از شهریه
+• شامل مبلمان، قبوض، اینترنت، فعالیت‌های ساکنان و بیمهٔ مستأجر</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>• سیکل 2026/27: صفحه از ≈ دسامبر ۲۰۲۵ «Applications are open» بود
+• درخواست‌های تا ۱۰ فوریه وارد قرعهٔ time slot (انتخاب اتاق) می‌شوند
+• تاریخ‌های ۲۰۲۷ هنوز منتشر نشده — احتمالاً مشابه (تأییدنشده)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>• درخواست CAD 65 (غیرقابل‌برگشت)
+• advance payment برای قبول offer: سال‌اولی‌ها CAD 1,000؛ مبلغ ارشد پیدا نشد
+• بازپرداخت در صورت رد ویزا: ذکر نشده</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>• ۸ ماه (سپتامبر–آوریل)
+• تابستان 2026 جدا، هر ترم (۳ مه–۲۲ ژوئن و ۲۸ ژوئن–۱۶ اوت): Crowsnest استودیو CAD 2,795 · یک‌خوابه 2,985 · دوخوابه 2,306
+• meal plan فقط برای سال‌اولی‌ها اجباری است</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>دوخوابهٔ مشترک Crowsnest ارزان‌ترین خوابگاهِ ارشد در هر ۸ دانشگاه است (≈ CAD 1,153 در ماه)</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027
+https://www.ucalgary.ca/ancillary/residence/live-us/places-live/graduate/crowsnest-hall
+https://www.ucalgary.ca/ancillary/residence/live-with-us/application-information/application-process</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>رتبه‌های اتاوا/مک‌مستر/دالهاوزی/ویکتوریا (QS 2027)</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>https://www.idp.com/vietnam/study-in-canada/top-universities-in-canada/?lang=en</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>رسمیِ رتبه‌بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>۳</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>uOttawa — اتاوا</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>• ساختمان ویژهٔ ارشد ندارد؛ ارشدها برای همان قراردادهای عمومی درخواست می‌دهند
+• ۱۲ ماهه (سپتامبر–اوت): Hyman Soloway (روی کمپوس، ۲۳۹ تخت، اتاق در آپارتمان ۲–۴ خوابه)، 45 Mann (کنار کمپوس، حمام خصوصی)، Annex
+• ۸ ماهه: Rideau و Friel (غذا اختیاری)؛ سنتی‌ها، Henderson و 90 University با meal plan اجباری</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — تضمین بین‌المللی فقط برای «کارشناسی تمام‌وقت یا graduate diploma» است (متن Fall 2026)؛ master مشمول نیست
+• تضمین کانادایی‌ها هم فقط کارشناسیِ سال اول</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>جدا — اقساط خوابگاه (پاییز ۲۰۲۶: ۲ اکتبر · زمستان ۲۰۲۷: ۲۹ ژانویه؛ ۱۲ماهه‌ها قسط تابستانی هم دارند — در سیکل قبل ۲۲ مه)
+• Hyman Soloway: گرما، برق، Wi-Fi و تهویه شامل است؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>• ۸ دسامبر ۲۰۲۶ ساعت ۹ صبح (وقت اتاوا): شروع درخواستِ تازه‌پذیرفته‌شده‌ها، بعد از دریافت offer
+• به غیرتضمینی‌ها offer از اواسط ژوئن شروع می‌شود و تا تابستان ادامه دارد؛ ترتیب = اولین‌نفر
+• اگر تا اواسط ژوئیه offer نگرفتید، خود دانشگاه می‌گوید بازار بیرون را بگردید</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>• ودیعهٔ CAD 950 (قواعد 2026–27)
+• بازگشت: تا ۱۵ ژوئن ۱۰۰٪ منهای CAD 105؛ تا ۳۰ ژوئن ۵۰٪؛ بعدش صفر
+• مبلغ به student account برمی‌گردد (برای برگشت به کارت باید فرم بدهید)
+• رد ویزا: ذکر نشده</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>• ۱۲ ماه (سپتامبر–اوت) برای Hyman Soloway، 45 Mann و Annex
+• ۸ ماه (سپتامبر–آوریل) برای بقیه</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ شمول قبوض در 45 Mann و Annex تأیید نشد (فقط Hyman Soloway)
+⚠️ تاریخ‌ها و ودیعهٔ ۲۰۲۷–۲۸ هنوز منتشر نشده</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/compare-residences
+https://www.uottawa.ca/campus-life/housing/hyman-soloway
+https://www.uottawa.ca/campus-life/housing/apply-residence
+https://www.uottawa.ca/campus-life/housing/dates-deadlines</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="115" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>اعلام رتبهٔ ۲۰۲۷ و افت کلگری</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>https://dailyhive.com/calgary/university-of-calgary-top-universities-2027</t>
+          <t>۴</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>McMaster — همیلتون</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>خبری</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>• 10 Bay — خوابگاهِ McMaster در پایین‌شهر همیلتون (برج ۳۰ طبقه، ۶۴۴ اتاق، شاتل مستقیم به کمپوس)؛ ارشد، پسادکتری، کارشناسی و کارکنان
+• خوابگاه‌های داخل کمپوس: اولویت با تازه‌دیپلمه‌هاست (FAQ رسمی)؛ ساختمان جدای ارشد در کمپوس پیدا نکردم</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ ذکر نشده — تضمین یا لیست انتظار در صفحه‌ها نیامده؛ ولی ورود آسان است: بدون ودیعه، بدون اجارهٔ اولین/آخرین ماه، بدون چک اعتباری و سابقهٔ اجاره</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>جدا — اجارهٔ ماهانه مستقیماً روی McMaster student account می‌نشیند، نه شهریه
+• شامل مبلمان، گرما، آب، برق، Wi-Fi و شاتل</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>• رولینگ؛ تاریخ مشخص پیدا نشد (سایت 10bayliving.ca برای من لود نشد؛ فقط خلاصهٔ جست‌وجو)
+• اپلای از طریق Residence Application و Housing Portal (پیش‌نیازِ پذیرش در صفحه‌ها ذکر نشده)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>• ودیعه ندارد؛ اجارهٔ اولین/آخرین ماه ندارد (صفحهٔ رسمی)
+• قرارداد ۱۲ ماهه: شرایط لغو زودهنگام در صفحه‌ها نیامده</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>• ۱۲ ماه، از اول هر ماه؛ گزینهٔ چندساله هم هست</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ قیمت‌ها سال ندارند (صفحهٔ مک‌مستر ژوئن ۲۰۲۵؛ همان اعداد در آگهی‌های مه ۲۰۲۶)؛ یک‌خوابه در آگهی‌ها تا CAD 2,426 (ثانویه)</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/
+https://housing.mcmaster.ca/graduate-residence/10bayapply/
+https://10bayliving.ca/faqs/
+https://housing.mcmaster.ca/residence-faq/
+https://news.mcmaster.ca/mcmasters-graduate-residence-means-new-housing-options-for-students/</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="190" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>کلگری — صفحهٔ رسمی نرم‌افزار (ساختار، اینترنشیپ ۸–۱۶ ماهه، بدون استاد)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>https://grad.ucalgary.ca/future-students/graduate/discover-opportunities/explore-programs/electrical-and-computer-engineering-meng-software-course</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>۵</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Dalhousie — هالیفاکس</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>• Graduate House — فقط ۱۳ نفر؛ Sexton Campus؛ تک‌اتاق؛ بدون RA
+• Glengary Apartments — ۴۰ نفر؛ ۱۲ آپارتمان سه‌اتاقه + ۴ bachelor؛ (returning و transfer)
+• سنتی‌ها (Howe، Shirreff، Gerard، Risley، LeMarchant) برای کارشناسی با meal plan اجباری</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — «New student room guarantee» فقط برای تازه‌دیپلمه‌هاست؛ تخصیص اتاق اولین‌نفر</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>جدا — روی همان student account (قسط پاییز ۲۲ سپتامبر 2026)؛ شامل Wi-Fi، گرما، آب و برق
+• meal plan در Graduate House و Glengary اختیاری است</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>• درخواست‌های 2027/28: ≈ ۱ اکتبر ۲۰۲۶ (tentative)
+• مهلت اول ۲ دسامبر ۲۰۲۶ فقط برای returning residents (≤ ۲۵۰ جا)؛ بقیه اولین‌نفر تا پر شدن
+• باید دانشجوی تمام‌وقت و پذیرفته‌شده باشید</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>• درخواست CAD 50 (غیرقابل‌برگشت)
+• ودیعهٔ تأیید اتاق CAD 500 — غیرقابل‌برگشت؛ استیناف فقط برای شرایط خارج از کنترل (پزشکی/خانوادگی)؛ «رد ویزا» ذکر نشده</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>• ۸ ماه (سپتامبر–آوریل)
+• summer residence جدا</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>ظرفیت ناچیز (≈ ۵۳ تخت برای همهٔ returning/transfer/ارشد)
+⚠️ دو صفحه ددلاین تضمینِ تازه‌دیپلمه را ۱ مه و ۱۵ مه نوشته‌اند (به ارشد ربطی ندارد، فقط ناهماهنگی)</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/costs-fees.html
+https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/important-dates-deadlines.html
+https://www.dal.ca/life-at-dal/housing/apply-for-residence/accepting-room-offer.html
+https://www.dal.ca/life-at-dal/housing/apply-for-residence.html
+https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/grad-house.html
+https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/glengary-apartments.html</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="145" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>کلگری — برنامهٔ اینترنشیپ شولیش</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>https://schulich.ucalgary.ca/current-students/engineering-career-centre/meng-internship</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>۶</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>UVic — ویکتوریا</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>• قرعهٔ ارشد برای Fall 2027: ≈ ۵۰ جا
+• ارشدها در تابستان به cluster (۴ و ۲ خوابه)، آپارتمان (bachelor/یک‌خوابه) و pod دسترسی دارند؛ برای سال تحصیلی صفحهٔ ارشد نوع اتاق را نمی‌گوید — Kaplan (ثانویه): یک‌خوابه برای ارشد، cluster/pod برای کارشناسیِ سال‌بالا
+• dormitory (با meal plan اجباری) برای تازه‌دیپلمه‌هاست</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — قرعه؛ صفحه می‌گوید فضای ارشد محدود است؛ تضمین فقط سال‌اولیِ تازه‌دیپلمه</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>جدا — قرارداد Residence Services (قسط‌ها: ۱ اوت و ۱۵ نوامبر در 2026–27)
+• شامل گرما، آب گرم، برق و اینترنت؛ meal plan در آپارتمان و cluster اختیاری</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>• درخواست از اولین دوشنبهٔ اکتبر ساعت ۹ صبح PDT = ۵ اکتبر ۲۰۲۶
+• ددلاین ورود به قرعه ۱۵ مه ۲۰۲۷ — فقط با درخواست ۸ ماهه (سپتامبر–آوریل)؛ بعد از ۱۵ مه یا فقط-ترم-پاییز = لیست انتظار
+• offerها از ۱۵ مه تا اواخر اوت؛ ۴۸ ساعت برای پذیرش</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>• درخواست CAD 50 (غیرقابل‌برگشت)
+• بعد از offer: acceptance fee CAD 1,000 (قرارداد 2026–27؛ از اجارهٔ ترم کم می‌شود، غیرقابل‌برگشت) + CAD 250 security deposit
+• رد ویزا: ذکر نشده
+• bursary تا CAD 1,500 فقط برای کانادایی‌هاست</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>• ۸ ماه (سپتامبر–آوریل)
+• تابستان 2026 جدا (حداقل ۳۰ شب): bachelor CAD 1,334 + CAD 44.47 هر شب اضافه؛ یک‌خوابه CAD 1,666 + CAD 55.53</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ نوع اتاقِ ارشد در سال تحصیلی تأیید رسمی ندارد (از جدول تابستان و Kaplan برداشت شد)</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php
+https://www.uvic.ca/residence/future-residents/apply/graduate/index.php
+https://www.uvic.ca/residence/assets/docs/residence-contract-2026-27.pdf
+https://www.uvic.ca/residence/future-residents/apply/summer/index.php</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>کلگری — شهریهٔ رسمی 2026/27 (برای تطبیق نرخ درسی)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>https://calendar.ucalgary.ca/</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>۷</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Carleton — اتاوا</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>• Leeds House طبقهٔ ۵ و ۶ — مخصوص ارشد؛ بیشتر سوئیت‌های دونفره (دو تک‌اتاق + یک سرویس) و یک سوئیت چهارنفره در هر طبقه؛ co-ed؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>❌ ندارد — صف؛ در 2026–27 «Residence is currently full» است
+• صف: اگر تا ۲ اکتبر ۲۰۲۶ offer نیاید درخواست منقضی می‌شود
+• تضمین فقط سال‌اولیِ تازه‌دیپلمه</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>جدا — روی student account؛ شامل اتاق، قبوض، اینترنت، حق عضویت Graduate Residence Council و بیمهٔ مستأجر (+ غذا اگر بخواهید)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>• سیکل 2026–27: درخواست‌ها از ۲ فوریه ۲۰۲۶ باز شد؛ time ticket ۲۳ فوریه؛ انتخاب اتاق از ۳ مارس
+• پیش‌نیاز: پذیرش در برنامهٔ ارشد (تمام‌وقت) و accept کردن offer؛ وضعیت «Applicant Acceptance» ۳–۴ روز بعد دیده می‌شود
+• ۲۰۲۷: انتظار می‌رود مشابه (اوایل فوریه) — تأییدنشده</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>• درخواست CAD 50 (غیرقابل‌برگشت)
+• Residence Advance Payment CAD 700 (قسط اول اجارهٔ خوابگاه)؛ شرایط بازگشتش برای ارشد در صفحه نیامده</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>• ۸ ماه (سپتامبر–آوریل)
+• تابستان 2026: کل تابستان (۵ مه–۲۴ اوت) CAD 4,218؛ هر نیمه CAD 2,052؛ غذای تابستانی اختیاری CAD 3,190 (کل)
+• «Guaranteed 12-Month Residence for International Students» (از سپتامبر ۲۰۲۵): ۸ ماه تضمین‌شده + تمدید تابستانی با درخواست جدا — صراحتاً شامل ارشد نمی‌گوید</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>ارشد اولویت ندارد و Leeds تنها خوابگاه ارشد است
+⚠️ شمول «12-month guaranteed» برای ارشد تأییدنشده</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/fees/
+https://housing.carleton.ca/future-residents/apply-to-residence/
+https://housing.carleton.ca/buildings/leeds-house/</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>آلبرتا — توقف ارشد درسی کامپیوتر از ۲۰۲۱ + ددلاین‌ها</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>https://www.ualberta.ca/en/computing-science/graduate-studies/programs-and-admissions/applications-and-admissions/index.html</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>آلبرتا — ارشد مالتی‌مدیا با اینترنشیپ</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>https://www.ualberta.ca/en/graduate-programs/master-of-science-in-computing-science-with-a-specialization-in-multimedia-computing-science.html</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>آلبرتا — شرایط پذیرش ارشد برق/نرم‌افزار (معدل ۳.۰ در ۶۰ واحد آخر)</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>https://www.idp.com/universities-and-colleges/university-of-alberta/master-of-engineering-in-electrical-and-computer-engineering-software-engineering-and-intelligent-systems/PRG-CA-00458429/</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>اتاوا — کوآپ ارشد اختیاری/ظرفیت محدود</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>https://www.applyboard.com/schools/university-of-ottawa/programs/master-of-engineering-electrical-and-computer-engineering-course-optional-co-op</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>اتاوا — ادعای «دومین کوآپ بزرگ انتاریو» (کارشناسی)</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.uottawa.ca/faculty-engineering/undergraduate-studies/programs</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>مک‌مستر — کوآپ/تجربهٔ کاری ارشد مهندسی (۴–۱۲ ماه)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>https://academiccalendars.romcmaster.ca/preview_program.php?catoid=48&amp;poid=24729&amp;returnto=9558</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>مک‌مستر — شهریه و شرایط ارشد کامپیوتر</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mastersportal.com/studies/124712/computing-and-software.html</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>دالهاوزی — جدول شهریهٔ ارشد 2026/27 (مبنای $47,984 مک‌آپ‌سی)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>https://www.dal.ca/admissions/graduate/tuition-fees.html</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>دالهاوزی — ساختار سه‌استریمی مک‌آپ‌سی و آیلتس ۷</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>https://www.dal.ca/faculty/computerscience/graduate-programs/master-of-applied-computer-science.html</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>ویکتوریا — صفحهٔ ارشد برق و کامپیوتر (کوآپ اختیاری، کف معدل)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-victoria-uvic/postgrad/electrical-computer-engineering-meng-taught</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>ویکتوریا — شهریه/آیلتس/ددلاین</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>https://collegedunia.com/canada/university/105-university-of-victoria-victoria/master-of-engineering-meng-electrical-and-computer-engineering-193222</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>کارلتون — شهریهٔ ارشد برق و کامپیوتر</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>https://collegedunia.com/canada/university/2-carleton-university-ottawa/master-of-engineering-meng-electrical-and-computer-engineering-15450</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>کارلتون — کوآپ تا ۸ ماه در برنامه‌های کامپیوتر</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mastersportal.com/studies/61188/computer-science.html</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — رتبهٔ QS 2027 (=546)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>https://www.topuniversities.com/universities/university-guelph</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>رسمیِ رتبه‌بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — THE 2027 (451–500) و THE Computer Science 2026 (301–400)</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>https://www.timeshighereducation.com/world-university-rankings/university-guelph</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>رسمیِ رتبه‌بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — رتبهٔ QS 2026 (504)</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/cbs/news/2026/03/university-guelph-retains-global-ranking-biological-sciences-anatomy-physiology-2026-qs</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — MSc Computer Science (شرایط، ددلاین‌های ۲۰۲۷، فاندینگ CAD 20,000)</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/programs/msc-computer-science</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — MASc مهندسی (شرایط، ددلاین، IELTS، فاندینگ S26+ = CAD 35,500)</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/programs/masc-engineering/</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — فاندینگ مهندسی (S25+ = CAD 23,400؛ MEng بدون فاندینگ)</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/engineering/future/graduate-funding/</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — MEng (۱۲–۱۶ ماه، WEX اختیاری، ددلاین‌ها، کف ۷۰٪)</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/programs/master-of-engineering/</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — WEX (حداقل ۱۰ هفته و ۳۵۰ ساعت، سه درس)</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/experiential-learning/current-students/wex</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — Master of Data Science (درسی، ۱۲–۱۶ ماه)</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/programs/master-of-data-science</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — جدول شهریهٔ سالانهٔ ۲۰۲۶/۲۷ و ۲۰۲۷/۲۸، برآورد هزینهٔ زندگی، UHIP، خوابگاه</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>https://graduatestudies.uoguelph.ca/future/cost</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — شهریهٔ هر ترم و هزینه‌های اجباری ۲۰۲۶/۲۷</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/registrar/finances-fees/tuition-fees/guelph-grad</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — جدول نمرات زبان انگلیسی</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>https://graduatestudies.uoguelph.ca/future/international/english</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — معادل‌سازی مدرک ایران (کارشناسی ۴ ساله پذیرفته)</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>https://graduatestudies.uoguelph.ca/future/international/credential</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — جدول نمره‌دهی ایران (Scholaro: B = 14–16.99؛ مرجعِ ارجاعیِ خود Guelph)</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.scholaro.com/db/Countries/Iran/Grading-System</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>ثانویه</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — مراحل اپلای و اپلیکیشن‌فی CAD 125</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>https://graduatestudies.uoguelph.ca/future/applying-guelph</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — مدارک اپلای (اعتبار ۲ سالهٔ نمرهٔ زبان، ترجمهٔ رسمی)</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>https://graduatestudies.uoguelph.ca/future/apply/documents</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Guelph — حوزه‌های تحقیقاتی و استادهای SoCS</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/computing/future/graduate-studies/</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Guelph — تخصص مشترک AI و بورس Vector (CAD 17,500)</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>https://www.uoguelph.ca/programs/csai/</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>تمکن مالی مجوز تحصیل — $16,500 (سپتامبر ۲۰۲۶، خارج کبک)</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/immigration-refugees-citizenship/services/study-canada/study-permit/prepare/proof-funds.html</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>رسمی</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>تحلیل کامل قبلی (بخش ۲۸: کانادا با اعداد رسمی)</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>Migration-Analysis.md در همین ریپو</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>داخلی</t>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Guelph — گوئلف</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>• West Village (۷۸ College Ave W): تاون‌هاوس ۲–۳ خوابه و آپارتمان ۲ خوابه؛ «ارشد» صراحتاً در مشخصات آمده؛ meal plan اختیاری؛ اینترنت و لاندری داخل
+• ساختمان‌های سنتی (South، Mills، …): meal plan اجباری</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>✅ دارد — «دانشجوی بین‌المللیِ جدیدِ master تضمین خوابگاه دانشگاه را تا پایان دورهٔ تحصیل دارد» (متن Fall 2027–Winter 2028)
+• شرط: درخواست + ودیعهٔ CAD 750 + قبول پذیرش — هر سه تا ۱ ژوئن
+• PhD بین‌المللی: فقط سال اول؛ ارشد کانادایی: بدون تضمین (لیست انتظار)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>جدا از شهریه و هزینه‌های اجباری؛ همه روی student account (فقط ودیعه با کارت در Housing Portal)
+• اینترنت، لاندری، مبلمان داخل است</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>• Fall 2027–Winter 2028: باز شدن ۱ فوریه ۲۰۲۷
+• برای درخواست باید offer پذیرش داشته باشید؛ ودیعه تا ۱ ژوئن لازم نیست</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>• ودیعهٔ CAD 750 (به Winter 2028 می‌رود؛ بعد از تضمین غیرقابل‌برگشت؛ استثناها: لغو در صف/لیست انتظار، ابطال پذیرش، تعویق)
+• رد ویزا جزو استثناها نیست (استیناف برای شرایط خاص)
+• جانبی: IHC CAD 28.84 در ترم؛ ماندن در تعطیلات زمستان +CAD 500؛ ورود/خروج زودتر CAD 40 در شب؛ Temporary Expanded Space CAD 3,500 در ترم</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>• ۸ ماه (سپتامبر–آوریل)؛ تعطیلات زمستان خارج از قرارداد
+• تابستان 2026 جدا: تاون‌هاوس تک‌اتاق CAD 2,500 · آپارتمان یک‌نفره 3,000 · اتاق در دوخوابه 2,750 · دونفره 2,500</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ نرخ‌ها tentative‌اند (۲۰۲۷–۲۸ را هیئت امنا بهار ۲۰۲۷ تعیین می‌کند)
+⚠️ تضمین، نوع یا ساختمان اتاق را مشخص نمی‌کند (ساختمان سنتی = meal plan اجباری)
+تنها دانشگاهِ این جدول با تضمین ارشدِ بین‌المللی</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/apply
+https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/west-village
+https://www.uoguelph.ca/housing/communities/compare-communities</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>راهنما: ✅ تضمین دارد · ❌ ندارد · ⚠️ ذکر نشده/مشروط. همهٔ مبالغ CAD‌اند (دلار در شیت «خوابگاه — قیمت‌ها»). ودیعه و رد ویزا: فقط Alberta صریحاً بازپرداخت را می‌نویسد؛ Guelph، Dalhousie و UVic غیرقابل‌برگشت‌اند و «رد ویزا» را استثنا نکرده‌اند، uOttawa فقط تا ۳۰ ژوئن، 10 Bay ودیعه ندارد — قبل از پرداخت کتباً بپرسید. نکتهٔ سیاست: خوابگاه ظرفیت کم و قرعه/صف دارد (Dal ≈ ۵۳ تخت، UVic ≈ ۵۰ جا، Carleton امسال پر)؛ جز Guelph و Alberta روی آن به‌عنوان برنامهٔ اصلی حساب نکنید؛ برنامهٔ ب = اتاق خصوصی (شیت «خوابگاه و مسکن» در Table_final).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3167,7 +3096,3944 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="58" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>قیمت خوابگاه ارشد — هر عدد با منبع و تاریخ (CAD؛ دلار با 0.705)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>بازدید ۲ اکتبر ۲۰۲۶ · «کل قرارداد» ≈ یعنی محاسبه (ماهانه × ماه) · «ماهانه» = کل ÷ ماه‌های قرارداد · دلار = CAD × 0.705 و گرد شده · «٪ بودجه» = ماهانهٔ خوابگاه ÷ بودجهٔ ماهانهٔ کل زندگی در مدل (بازهٔ شهر) · «اختلاف» = خوابگاه − اتاق خصوصیِ همان شهر در Table_final (CAD در ماه؛ + یعنی خوابگاه گران‌تر) · نرخ 2027–28 هنوز منتشر نشده؛ در Calgary و uOttawa سال‌به‌سال +2.5٪ تا +6٪ بوده (قاعدهٔ حکم در شیت «مفروضات و هشدارها»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>دانشگاه</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>گزینه (ساختمان — نوع اتاق)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>قرارداد (ماه)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>کل قرارداد (CAD)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ماهانه (CAD)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ماهانه (USD)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>شامل چه؟</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>وضع عدد</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>٪ بودجهٔ ماهانهٔ مدل</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>اختلاف با اتاق خصوصی (CAD/ماه)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>حکم نسبت به بودجهٔ مدل</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>منبع رسمی (نشانی)</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>تاریخ بازدید</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Graduate Residence — اتاق در آپارتمان مشترک</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>۱۱ (قرارداد اول؛ تمدیدها ۱۲)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>≈ 14,685</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1,335</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>گرما/آب/برق/اینترنت: برای Graduate Residence تصریح نشده (HUB: شامل)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>74–89٪</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>+335 تا +635</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/unit-types.html
+https://www.ualberta.ca/en/residence/our-residences/graduate-residence.html</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Graduate Residence — استودیو</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>۱۱ (قرارداد اول؛ تمدیدها ۱۲)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>≈ 17,545</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>1,595</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>1,124</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>89–106٪</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>+595 تا +895</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/unit-types.html
+https://www.ualberta.ca/en/residence/our-residences/graduate-residence.html</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>HUB — استودیو (ماه‌به‌ماه)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ماه‌به‌ماه</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1,595</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>1,124</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>اینترنت بی‌سیم، گرما، آب، برق</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>89–106٪</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>+595 تا +895</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/hub.html
+https://www.ualberta.ca/en/residence/our-residences/unit-types.html</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>HUB — یک‌خوابه (ماه‌به‌ماه؛ زوج‌ها مجازند)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ماه‌به‌ماه</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>1,996</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>1,407</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>اینترنت بی‌سیم، گرما، آب، برق</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>111–133٪</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>+996 تا +1,296</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/hub.html
+https://www.ualberta.ca/en/residence/our-residences/unit-types.html</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Calgary</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Crowsnest Hall — اتاق در آپارتمان دوخوابه (مشترک)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>9,224</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1,153</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>مبلمان، قبوض، اینترنت، بیمهٔ مستأجر؛ meal plan ندارد</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>58–70٪</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>−47 تا +353</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Calgary</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Crowsnest Hall — استودیو</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>11,178</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>1,397</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>70–85٪</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>+197 تا +597</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Calgary</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Crowsnest Hall — یک‌خوابه</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>11,937</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1,492</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1,052</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>75–90٪</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>+292 تا +692</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Calgary</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Crowsnest — تابستان 2026، هر ترم ≈۷ هفته (استودیو 2,795 · یک‌خوابه 2,985 · دوخوابه 2,306)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>تابستان (۲ ترم)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2,306–2,985 (کل ترم)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>uOttawa</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Hyman Soloway — اتاق در آپارتمان ۴خوابه</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>۱۲ (سپتامبر–اوت)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>15,601</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>1,300</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>گرما، برق، Wi-Fi، تهویه؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>59–72٪</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>+100 تا +500</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/hyman-soloway
+https://www.uottawa.ca/campus-life/housing/compare-residences</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>uOttawa</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Hyman Soloway — اتاق در آپارتمان ۳خوابه</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>۱۲ (سپتامبر–اوت)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>16,501</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>1,375</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>63–76٪</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>+175 تا +575</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/hyman-soloway</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>uOttawa</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hyman Soloway — اتاق در آپارتمان ۲خوابه</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>۱۲ (سپتامبر–اوت)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>18,757</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1,563</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1,102</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>71–87٪</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>+363 تا +763</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/hyman-soloway</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>uOttawa</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>45 Mann — اتاق تک با حمام خصوصی (دامنهٔ قیمت)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>۱۲ (سپتامبر–اوت)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>16,600–26,308</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>1,383–2,192</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>975–1,546</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>شمول قبوض تأیید نشد؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>63–122٪</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>+183 تا +1,392</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/compare-residences</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>uOttawa</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Annex — اتاق (دامنهٔ قیمت)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>۱۲ (سپتامبر–اوت)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>15,574–27,304</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>1,298–2,275</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>915–1,604</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>شمول قبوض تأیید نشد؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>59–126٪</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>+98 تا +1,475</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/compare-residences</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>10 Bay — اتاق در دوخوابه (Standard)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>۱۲ (از اول هر ماه)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>≈ 16,992</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>1,416</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>مبله، گرما/آب/برق، Wi-Fi، شاتل؛ بدون ودیعه</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>83–101٪</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/
+https://housing.mcmaster.ca/graduate-residence/10bayapply/</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>10 Bay — اتاق در دوخوابه (Premium)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>۱۲ (از اول هر ماه)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>≈ 18,516</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>1,543</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>1,088</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>91–110٪</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>10 Bay — استودیو (Basic / Standard / Premium)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>۱۲ (از اول هر ماه)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>≈ 23,040–23,484</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>1,920–1,957</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>1,354–1,380</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>113–140٪</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>McMaster</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>10 Bay — یک‌خوابه</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>۱۲ (از اول هر ماه)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>≈ 25,512</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>2,126</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>1,499</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا (آگهی‌ها تا 2,426 — ثانویه)</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>رسمی؛ سال نرخ ذکر نشده</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>125–152٪</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Dalhousie</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Graduate House — تک‌اتاق</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>10,606</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>1,326</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Wi-Fi، گرما، آب، برق؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>66–80٪</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>+226 تا +576</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/costs-fees.html
+https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/grad-house.html</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Dalhousie</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Glengary — تک‌اتاق در آپارتمان ۳خوابه</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>10,761</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>1,345</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>67–82٪</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>+245 تا +595</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/costs-fees.html
+https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/glengary-apartments.html</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Dalhousie</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Glengary — bachelor</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>12,684</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>1,586</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>1,118</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>79–96٪</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>+486 تا +836</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/costs-fees.html
+https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/glengary-apartments.html</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>UVic</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Cluster — اتاق در واحد ۴خوابه</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>10,330</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>1,291</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>گرما، آب گرم، برق، اینترنت؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>56–68٪</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>−9 تا +391</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>UVic</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor apartment</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>10,374</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>1,297</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>56–68٪</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>−3 تا +397</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php
+https://www.uvic.ca/residence/assets/docs/residence-contract-2026-27.pdf</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>UVic</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>One-bedroom apartment</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>12,954</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>1,619</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>1,142</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>70–85٪</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>+319 تا +719</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>UVic</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Cluster — اتاق در تاون‌هاوس ۲خوابه</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>13,432</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>1,679</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>1,184</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>73–88٪</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>+379 تا +779</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ فشار</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Carleton</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Leeds House ۵–۶ (ارشد) — فقط اتاق</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>11,292</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1,412</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>اتاق، قبوض، اینترنت، حق عضویت GRC، بیمهٔ مستأجر؛ بدون غذا</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>64–78٪</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>+212 تا +612</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/fees/</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Carleton</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Leeds ۵–۶ — با meal plan Reduced (۱۰ وعده در هفته + CAD 300 Dining Dollars)</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>16,113</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2,014</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>1,420</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا + غذا</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>92–112٪</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>+814 تا +1,214</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/fees/</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Carleton</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Leeds ۵–۶ — با meal plan All Access (نامحدود + CAD 200 Dining Dollars)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>18,093</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2,262</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>1,594</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا + غذا</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>103–126٪</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>+1,062 تا +1,462</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>❌ از بودجه می‌زند</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/fees/</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Carleton</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>تابستان 2026 — کل تابستان (۵ مه–۲۴ اوت)، اتاق تک در سوئیت مشترک</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>تابستان (≈ ۳٫۷ ماه)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>4,218 (کل ترم)</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>غذای تابستانی اختیاری: CAD 3,190 (کل)</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/apply-to-residence/</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="55" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>West Village — اتاق تک در تاون‌هاوس</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>10,992</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>1,374</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>اینترنت، لاندری، مبلمان؛ meal plan اختیاری</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27 (tentative)</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>72–76٪</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/west-village</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="55" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>West Village — آپارتمان یک‌نفره</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>11,592</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>1,449</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>1,022</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27 (tentative)</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>76–80٪</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/west-village</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="55" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>West Village — اتاق در آپارتمان دوخوابه</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>11,042</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>1,380</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27 (tentative)</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>73–77٪</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/west-village</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="55" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>West Village — اتاق دونفره در آپارتمان</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>10,592</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>1,324</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27 (tentative)</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>70–74٪</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>✅ جا می‌شود</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/west-village</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="70" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ساختمان سنتی (South، Mills، …) — اتاق تک؛ meal plan اجباری و قیمتش پیدا نشد</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>۸ (سپتامبر–آوریل)</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>10,482</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>1,310</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>فقط اتاق؛ meal plan اجباری جداست (کل بالاتر از این)</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>رسمی 2026–27 (tentative)</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ کل = اتاق + meal plan اجباری (قیمت meal plan را پیدا نکردم)</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits
+https://www.uoguelph.ca/housing/communities/compare-communities</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="55" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>West Village — تابستان 2026 (تاون‌هاوس تک 2,500 · آپارتمان یک‌نفره 3,000 · دوخوابه 2,750 · دونفره 2,500)</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>ترم تابستان (طول در صفحه نیامده)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>2,500–3,000 (کل ترم)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>همان بالا</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>رسمی تابستان 2026</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>۲ اکتبر ۲۰۲۶</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="62" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>راهنما: آبی = رسمی 2026–27 · زرد = رسمیِ بدون سال یا tentative یا ناقص · حکم: ✅ سهم خوابگاه ≤ ٪۸۰ بودجهٔ ماهانه حتی در کم‌ترین بودجهٔ شهر · ❌ ≥ ٪۹۰ حتی در بیشترین بودجه · ⚠️ بین این دو (قاعدهٔ خودم، نه رقم دانشگاه). همیلتون و گوئلف اتاق خصوصی در جدول‌های ما ندارند، پس ستون اختلافشان «—» است. قراردادهای ۸ ماهه مه–اوت را پوشش نمی‌دهند؛ ردیف‌های تابستان جدا حساب شده‌اند.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>منابع راستی‌آزمی (بازدید ۱ اکتبر ۲۰۲۶؛ منابع Guelph و همهٔ ردیف‌های «خوابگاه»: ۲ اکتبر ۲۰۲۶)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>«رسمی» = صفحهٔ خود دانشگاه یا نهاد دولتی · «ثانویه» = سرویس‌های اپلای/اطلاعات دوره (شیکشا، مسترزپورتال، کالج‌دونیا، اپلای‌بورد، آی‌دی‌پی) — برای اپلای با صفحهٔ رسمی چک شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>موضوع</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>نشانی</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>وضع منبع</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>رتبهٔ آلبرتا — ۹۶ (QS 2027)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-alberta</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>رتبهٔ کلگری — ۲۴۹ (QS 2027)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-calgary</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>رتبه‌های اتاوا/مک‌مستر/دالهاوزی/ویکتوریا (QS 2027)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.idp.com/vietnam/study-in-canada/top-universities-in-canada/?lang=en</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>اعلام رتبهٔ ۲۰۲۷ و افت کلگری</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>https://dailyhive.com/calgary/university-of-calgary-top-universities-2027</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>خبری</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>کلگری — صفحهٔ رسمی نرم‌افزار (ساختار، اینترنشیپ ۸–۱۶ ماهه، بدون استاد)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>https://grad.ucalgary.ca/future-students/graduate/discover-opportunities/explore-programs/electrical-and-computer-engineering-meng-software-course</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>کلگری — برنامهٔ اینترنشیپ شولیش</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>https://schulich.ucalgary.ca/current-students/engineering-career-centre/meng-internship</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>کلگری — شهریهٔ رسمی 2026/27 (برای تطبیق نرخ درسی)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>https://calendar.ucalgary.ca/</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>آلبرتا — توقف ارشد درسی کامپیوتر از ۲۰۲۱ + ددلاین‌ها</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/computing-science/graduate-studies/programs-and-admissions/applications-and-admissions/index.html</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>آلبرتا — ارشد مالتی‌مدیا با اینترنشیپ</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/graduate-programs/master-of-science-in-computing-science-with-a-specialization-in-multimedia-computing-science.html</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>آلبرتا — شرایط پذیرش ارشد برق/نرم‌افزار (معدل ۳.۰ در ۶۰ واحد آخر)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.idp.com/universities-and-colleges/university-of-alberta/master-of-engineering-in-electrical-and-computer-engineering-software-engineering-and-intelligent-systems/PRG-CA-00458429/</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>اتاوا — کوآپ ارشد اختیاری/ظرفیت محدود</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>https://www.applyboard.com/schools/university-of-ottawa/programs/master-of-engineering-electrical-and-computer-engineering-course-optional-co-op</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>اتاوا — ادعای «دومین کوآپ بزرگ انتاریو» (کارشناسی)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/faculty-engineering/undergraduate-studies/programs</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>مک‌مستر — کوآپ/تجربهٔ کاری ارشد مهندسی (۴–۱۲ ماه)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>https://academiccalendars.romcmaster.ca/preview_program.php?catoid=48&amp;poid=24729&amp;returnto=9558</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>مک‌مستر — شهریه و شرایط ارشد کامپیوتر</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mastersportal.com/studies/124712/computing-and-software.html</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>دالهاوزی — جدول شهریهٔ ارشد 2026/27 (مبنای $47,984 مک‌آپ‌سی)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/admissions/graduate/tuition-fees.html</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>دالهاوزی — ساختار سه‌استریمی مک‌آپ‌سی و آیلتس ۷</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/faculty/computerscience/graduate-programs/master-of-applied-computer-science.html</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ویکتوریا — صفحهٔ ارشد برق و کامپیوتر (کوآپ اختیاری، کف معدل)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-victoria-uvic/postgrad/electrical-computer-engineering-meng-taught</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>ویکتوریا — شهریه/آیلتس/ددلاین</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/canada/university/105-university-of-victoria-victoria/master-of-engineering-meng-electrical-and-computer-engineering-193222</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>کارلتون — شهریهٔ ارشد برق و کامپیوتر</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>https://collegedunia.com/canada/university/2-carleton-university-ottawa/master-of-engineering-meng-electrical-and-computer-engineering-15450</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>کارلتون — کوآپ تا ۸ ماه در برنامه‌های کامپیوتر</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>https://www.mastersportal.com/studies/61188/computer-science.html</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — رتبهٔ QS 2027 (=546)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.topuniversities.com/universities/university-guelph</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — THE 2027 (451–500) و THE Computer Science 2026 (301–400)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>https://www.timeshighereducation.com/world-university-rankings/university-guelph</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>رسمیِ رتبه‌بند</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — رتبهٔ QS 2026 (504)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/cbs/news/2026/03/university-guelph-retains-global-ranking-biological-sciences-anatomy-physiology-2026-qs</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — MSc Computer Science (شرایط، ددلاین‌های ۲۰۲۷، فاندینگ CAD 20,000)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/msc-computer-science</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — MASc مهندسی (شرایط، ددلاین، IELTS، فاندینگ S26+ = CAD 35,500)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/masc-engineering/</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — فاندینگ مهندسی (S25+ = CAD 23,400؛ MEng بدون فاندینگ)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/engineering/future/graduate-funding/</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — MEng (۱۲–۱۶ ماه، WEX اختیاری، ددلاین‌ها، کف ۷۰٪)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/master-of-engineering/</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — WEX (حداقل ۱۰ هفته و ۳۵۰ ساعت، سه درس)</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/experiential-learning/current-students/wex</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — Master of Data Science (درسی، ۱۲–۱۶ ماه)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/master-of-data-science</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول شهریهٔ سالانهٔ ۲۰۲۶/۲۷ و ۲۰۲۷/۲۸، برآورد هزینهٔ زندگی، UHIP، خوابگاه</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/cost</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — شهریهٔ هر ترم و هزینه‌های اجباری ۲۰۲۶/۲۷</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/registrar/finances-fees/tuition-fees/guelph-grad</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول نمرات زبان انگلیسی</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/international/english</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — معادل‌سازی مدرک ایران (کارشناسی ۴ ساله پذیرفته)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/international/credential</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — جدول نمره‌دهی ایران (Scholaro: B = 14–16.99؛ مرجعِ ارجاعیِ خود Guelph)</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.scholaro.com/db/Countries/Iran/Grading-System</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>ثانویه</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — مراحل اپلای و اپلیکیشن‌فی CAD 125</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/applying-guelph</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — مدارک اپلای (اعتبار ۲ سالهٔ نمرهٔ زبان، ترجمهٔ رسمی)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>https://graduatestudies.uoguelph.ca/future/apply/documents</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Guelph — حوزه‌های تحقیقاتی و استادهای SoCS</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/computing/future/graduate-studies/</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Guelph — تخصص مشترک AI و بورس Vector (CAD 17,500)</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/programs/csai/</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>تمکن مالی مجوز تحصیل — $16,500 (سپتامبر ۲۰۲۶، خارج کبک)</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/immigration-refugees-citizenship/services/study-canada/study-permit/prepare/proof-funds.html</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — Unit Types: نرخ ماهانه (مشترک 1,335 · استودیو 1,595 · یک‌خوابه 1,996؛ سال ذکر نشده)</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/unit-types.html</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — Graduate Residence (۴ ساختمان، قرارداد ۱۱/۱۲ ماهه، فقط ارشد)</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/graduate-residence.html</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — HUB (ماه‌به‌ماه، شمول اینترنت/گرما/آب/برق)</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/our-residences/hub.html</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — درخواست (Fall 2027 باز است، CCID، CAD 25)</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/apply/index.html</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — Guaranteed Housing (فقط سال اول کارشناسی)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/apply/guaranteed-housing.html</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Alberta — لغو، ودیعه CAD 500 و بازپرداخت با رد ویزا</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ualberta.ca/en/residence/apply/cancellation-policy.html</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Calgary — نرخ 2026–27 (Crowsnest 11,178 / 11,937 / 9,224؛ تابستان؛ تاریخ اقساط)</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/rates-2026-2027</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Calgary — Crowsnest Hall (ارشد، قرعه، درخواست تا ۱۰ فوریه)</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-us/places-live/graduate/crowsnest-hall</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Calgary — فرایند درخواست (CAD 65، advance payment، تضمین سال‌اولی‌ها)</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca/ancillary/residence/live-with-us/application-information/application-process</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه uOttawa — مقایسهٔ خوابگاه‌ها و نرخ 2026–27 (۸ و ۱۲ ماهه)</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/compare-residences</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه uOttawa — Hyman Soloway (نرخ 2026–27، قبوض، ۲۳۹ تخت)</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/hyman-soloway</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه uOttawa — درخواست و تضمین (بین‌المللی: فقط کارشناسی/graduate diploma؛ شروع ۸ دسامبر)</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/apply-residence</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه uOttawa — تاریخ‌ها، ودیعه CAD 950 و جدول بازپرداخت</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca/campus-life/housing/dates-deadlines</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه McMaster — 10 Bay: قیمت ماهانه (سال ذکر نشده؛ متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/10bay-pricing/</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه McMaster — 10 Bay: شرایط اجاره (۱۲ ماه، بدون ودیعه، پرداخت روی student account)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/graduate-residence/10bayapply/</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه McMaster — 10 Bay: سؤال‌های متداول (کی می‌تواند اجاره کند)</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>https://10bayliving.ca/faqs/</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه McMaster — FAQ خوابگاه (اولویت تازه‌دیپلمه‌ها؛ 10 Bay برای سال‌بالا)</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.mcmaster.ca/residence-faq/</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه McMaster — خبر رسمی گشایش 10 Bay (۶۴۴ اتاق، ۲۰۲۳)</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>https://news.mcmaster.ca/mcmasters-graduate-residence-means-new-housing-options-for-students/</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — Costs and fees 2026/27 (Graduate House، Glengary)</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/costs-fees.html</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — تاریخ‌ها (درخواست‌های 2027/28 از ≈ ۱ اکتبر، tentative)</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/getting-started/important-dates-deadlines.html</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — پذیرش اتاق، ودیعه CAD 500 و استیناف</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence/accepting-room-offer.html</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — درخواست و ضمانت تازه‌دیپلمه (CAD 50)</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/apply-for-residence.html</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — Graduate House (۱۳ نفر)</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/grad-house.html</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Dalhousie — Glengary Apartments (۴۰ نفر؛ returning/transfer)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca/life-at-dal/housing/residences/halifax-campus/glengary-apartments.html</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه UVic — نرخ 2026–27 (bachelor/یک‌خوابه/cluster، شمول قبوض)</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/fees/index.php</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه UVic — قرعهٔ ارشد Fall 2027 (≈۵۰ جا، ۱۵ مه، شروع اولین دوشنبهٔ اکتبر)</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/apply/graduate/index.php</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه UVic — قرارداد 2026–27 (درخواست CAD 50، acceptance fee CAD 1,000)</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/assets/docs/residence-contract-2026-27.pdf</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (بخش‌هایی از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه UVic — تابستان: ارشد و نوع اتاق + نرخ</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uvic.ca/residence/future-residents/apply/summer/index.php</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Carleton — نرخ 2026–27 (Leeds ارشد: فقط اتاق / با غذا)</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/fees/</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Carleton — درخواست ارشد، صف، تابستان، «12-month» بین‌المللی</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/future-residents/apply-to-residence/</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Carleton — Leeds House (طبقهٔ ۵–۶ ارشد)</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>https://housing.carleton.ca/buildings/leeds-house/</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Guelph — درخواست و تضمین ارشد بین‌المللی (Fall 2027–Winter 2028)</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/apply</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Guelph — نرخ Fall 2026–Winter 2027 (tentative)، ودیعه $750، هزینه‌های جانبی</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/fees-deposits</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه Guelph — West Village (ارشد، meal plan اختیاری)</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/communities/west-village</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>رسمی</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>خوابگاه Guelph — مقایسهٔ ساختمان‌ها (meal plan اجباری در South)</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>https://www.uoguelph.ca/housing/communities/compare-communities</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>رسمی (متن از خلاصهٔ جست‌وجو)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>خوابگاه — مبنای مقایسه با مدل (بودجهٔ ماهانهٔ شهرها و اتاق خصوصی)</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Migration-Analysis.md §28.7 و Table_final.xlsx (شیت «خوابگاه و مسکن») در همین ریپو</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>داخلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>تحلیل کامل قبلی (بخش ۲۸: کانادا با اعداد رسمی)</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Migration-Analysis.md در همین ریپو</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>داخلی</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3352,19 +7218,91 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ددلاین MASc: بالای صفحه ۱۵ آوریل (بین‌المللی، Fall) ولی جدول ۲۰۲۶ همان صفحه ۱۵ مارس؛ SoCS برای Fall 2027 صریحاً ۱ مارس ۲۰۲۷ نوشته. مبنای ما: ۱ مارس. مدارک MASc تا یک ماه بعد از ددلاین پذیرفته می‌شود ولی توصیهٔ رسمی، اپلای ≥ ۹ ماه قبل از شروع است. خوابگاه تضمینی برای بین‌المللی‌ها در دادهٔ ۲۰۲۶ بود (درخواست و ودیعه تا ۱ ژوئن)؛ برای ۲۰۲۷ دوباره چک شود.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="78" customHeight="1">
+          <t>ددلاین MASc: بالای صفحه ۱۵ آوریل (بین‌المللی، Fall) ولی جدول ۲۰۲۶ همان صفحه ۱۵ مارس؛ SoCS برای Fall 2027 صریحاً ۱ مارس ۲۰۲۷ نوشته. مبنای ما: ۱ مارس. مدارک MASc تا یک ماه بعد از ددلاین پذیرفته می‌شود ولی توصیهٔ رسمی، اپلای ≥ ۹ ماه قبل از شروع است. خوابگاه: صفحهٔ رسمی Fall 2027–Winter 2028 (۲ اکتبر ۲۰۲۶) تضمین خوابگاه برای ارشدِ بین‌المللیِ جدید (master) را تا پایان دوره تأیید می‌کند — شرط: درخواست + ودیعهٔ CAD 750 + قبول پذیرش، هر سه تا ۱ ژوئن؛ جزئیات و ریسک ودیعه در شیت «خوابگاه».</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>خوابگاه — دامنه و تاریخ</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>شیت‌های «خوابگاه» و «خوابگاه — قیمت‌ها» (۲ اکتبر ۲۰۲۶، به درخواست شما): هشت دانشگاهِ همین فایل، فقط از صفحه‌های رسمی خود دانشگاه‌ها. نرخ‌ها 2026–27 هستند (برای ورودی‌های سپتامبر ۲۰۲۶)؛ نرخ ورودی شما (2027–28) هنوز در هیچ‌کدام منتشر نشده. روند سال‌به‌سال از جدول‌های رسمی خودشان (2025–26 ← 2026–27): Calgary Crowsnest +2.5٪ (استودیو و یک‌خوابه) و +5٪ (دوخوابه)؛ uOttawa Hyman Soloway +5.9٪ تا +6.0٪، 45 Mann +6.0٪، Annex +3.6٪ تا +6.0٪ → برای 2027–28 ≈ +3 تا +6٪ فرض کنید (برآورد من، تضمین نیست).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه — اعداد چطور ساخته شد</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>«ماهانه» = کل قرارداد ÷ ماه‌های قرارداد (۸ ماه = سپتامبر–آوریل؛ ۱۱ ماه برای Graduate Residence آلبرتا؛ ۱۲ ماه برای uOttawa و 10 Bay). فقط Alberta و 10 Bay قیمت ماهانهٔ رسمی دارند و «کل» از ماهانه × ماه‌ها محاسبه شده (با ≈ مشخص است). دلار = CAD × 0.705 (۲۹ سپتامبر ۲۰۲۶) و گرد شده. ماه‌های مه–اوت در قرارداد ۸ ماهه نیستند و جدا حساب می‌شوند (ردیف‌های تابستان).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="160" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>خوابگاه — مبنای مقایسه با مدل</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>«بودجهٔ ماهانهٔ مدل» = بازهٔ کل زندگی ماهانهٔ شهر در تحلیل قبلی (CAD): ادمونتون 1,500–1,800 · کلگری 1,650–2,000 · اتاوا 1,800–2,200 · همیلتون 1,400–1,700 · هالیفاکس 1,650–2,000 · ویکتوریا 1,900–2,300 · گوئلف 1,800–1,900. «اتاق خصوصی» = بازهٔ اتاق در خانهٔ مشترک در شیت «خوابگاه و مسکن» Table_final (CAD): ادمونتون 700–1,000 · کلگری و اتاوا 800–1,200 · هالیفاکس 750–1,100 · ویکتوریا 900–1,300؛ برای همیلتون و گوئلف رقمی نداریم و ستون اختلافشان «—» است. حکم: ✅ اگر سهم خوابگاه ≤ ٪۸۰ بودجه حتی در کم‌ترین بودجهٔ شهر؛ ❌ اگر ≥ ٪۹۰ حتی در بیشترین بودجه؛ ⚠️ بین این دو. این قاعده از خودم است، نه رقم دانشگاه، و بودجهٔ مدل را عوض نمی‌کند. (در پیام چت ادمونتون 650–1,000 را برای اتاق خصوصی گفته بودم؛ جدول Table_final 700–1,000 دارد و اینجا همان مبناست — اختلاف آلبرتا ۵۰ دلار کانادا کم می‌شود.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>خوابگاه — ودیعه و ویزا</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>فقط Alberta صریحاً می‌گوید با رد ویزا ودیعهٔ CAD 500 برمی‌گردد (اطلاع ظرف ۱۰ روز با نامهٔ رد). Guelph (CAD 750، بعد از تضمین)، Dalhousie (CAD 500) و UVic (acceptance fee CAD 1,000) غیرقابل‌برگشت‌اند و «رد ویزا» جزو استثناهایشان نیامده؛ uOttawa (CAD 950) فقط تا ۳۰ ژوئن برمی‌گرداند (۱۰۰٪ تا ۱۵ ژوئن منهای CAD 105)؛ 10 Bay ودیعه ندارد؛ شرط Calgary و Carleton برای ارشد پیدا نشد. قبل از پرداخت کتباً بپرسید. ویزای ایرانی‌ها دیر می‌رسد (ردیف «ویزا» همین شیت).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="160" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>خوابگاه — تأییدنشده‌ها</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Alberta: صفحهٔ Unit Types سال نرخ ندارد؛ نرخ صفحهٔ خود Graduate Residence لود نشد؛ شمول قبوض فقط در HUB تصریح شده؛ همان صفحه می‌گوید فقط «current U of A students» واجدند (CCID بعد از ثبت درخواست برنامه صادر می‌شود). McMaster: قیمت 10 Bay سال ندارد (همان اعداد در آگهی‌های مه ۲۰۲۶ است) و سایت 10bayliving.ca برایم لود نشد؛ ددلاین درخواست پیدا نشد. Calgary: advance payment ارشد و تاریخ‌های ۲۰۲۷ تأیید نشد. UVic: نوع اتاق ارشدها در سال تحصیلی از جدول تابستان و Kaplan (ثانویه) برداشت شد. Carleton: «Guaranteed 12-Month Residence for International Students» صراحتاً ارشد را نمی‌گوید. Guelph: نرخ‌ها tentative؛ تضمین نوع ساختمان را مشخص نمی‌کند (ساختمان سنتی = meal plan اجباری). Dalhousie: دو صفحه ددلاین تضمین تازه‌دیپلمه را ۱ و ۱۵ مه نوشته‌اند. uOttawa: شمول قبوض 45 Mann و Annex تأیید نشد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="100" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>اصلاح Table_final و گزارش</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>همین تاریخ ≈های خوابگاه Alberta/UVic/Carleton/Dalhousie در Table_final.xlsx (شیت «خوابگاه و مسکن») با اعداد رسمی جایگزین شد و جملهٔ «هیچ دانشگاهی ارشد بین‌المللی را تضمین نمی‌کند» (گزارش §28.7 و Table_final) با استثنای Guelph اصلاح شد (نسخهٔ ۳.۱۵ گزارش). بزرگ‌ترین اختلاف: Carleton با غذا — قبلاً ≈ $845–1,130 در ماه، رسمی $1,420–1,594 (Leeds با meal plan)؛ فقط‌اتاق $995. جملهٔ قبلی «Carleton با غذا اجباری است» هم برای Leeds غلط بود (meal plan اختیاری است).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="95" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>آنچه این فایل نیست</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>این فایل جایگزین چک‌لیست کانادا و شیت «تصمیم» در Table_final.xlsx نیست؛ فقط نسخهٔ اصلاح‌شدهٔ همان جدول ۷ ردیفی شماست. هشت درخواست اروپایی و مسیر پایان‌نامه‌ای موازات کانادا (تحلیل بخش ۲۸) سر جای خودشان باقی‌اند. ردیف ۸ (Guelph) بعداً، ۲ اکتبر ۲۰۲۶، به درخواست شما اضافه شد.</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>این فایل جایگزین چک‌لیست کانادا و شیت «تصمیم» در Table_final.xlsx نیست؛ فقط نسخهٔ اصلاح‌شدهٔ همان جدول ۷ ردیفی شماست. هشت درخواست اروپایی و مسیر پایان‌نامه‌ای موازات کانادا (تحلیل بخش ۲۸) سر جای خودشان باقی‌اند. ردیف ۸ (Guelph) بعداً، ۲ اکتبر ۲۰۲۶، به درخواست شما اضافه شد. شیت‌های «خوابگاه» و «خوابگاه — قیمت‌ها» هم همان روز، به درخواست شما، اضافه شدند.</t>
         </is>
       </c>
     </row>
